--- a/data/output/evaluasi_73.xlsx
+++ b/data/output/evaluasi_73.xlsx
@@ -8,15 +8,30 @@
   </bookViews>
   <sheets>
     <sheet name="7300" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="7317" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="7316" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="7372" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="7304" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="7312" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="7313" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="7310" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="7303" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="7306" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="7372" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="7306" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="7317" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="7309" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="7311" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="7310" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="7302" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="7307" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="7312" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="7313" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="7373" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="7314" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="7315" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="7318" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="7301" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="7304" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="7316" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="7325" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="7371" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="7303" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="7305" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="7322" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="7326" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="7308" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,7 +499,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-11.46461490529169</v>
+        <v>-17.68681834751242</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -493,7 +508,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -512,7 +527,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>62.0051776380012</v>
+        <v>25.99305977247928</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -521,7 +536,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -536,20 +551,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-15.97252325560564</v>
+        <v>5.51747262023279</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25</t>
+          <t>adhb_pi_q3-25</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -564,20 +579,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q1-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-44.48006419072827</v>
+        <v>-10.38531679111486</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q2-25</t>
+          <t>adhb_net_ekspor_q1-25</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -592,20 +607,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-10.60516825348064</v>
+        <v>-42.15539369211368</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25</t>
+          <t>adhb_net_ekspor_q2-25</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -620,20 +635,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>77.94285291773339</v>
+        <v>-31.65840394117055</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>adhk_pi_q2-25</t>
+          <t>adhb_net_ekspor_q3-25</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -652,16 +667,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-12.55644729990311</v>
+        <v>-10.02265712705795</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q1-25</t>
+          <t>adhk_pi_q1-25</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -680,16 +695,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-22.95052383151114</v>
+        <v>24.51708771037342</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q2-25</t>
+          <t>adhk_pi_q2-25</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -704,20 +719,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.2604132779943358</v>
+        <v>29.48681656823268</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>distribusi_pi_q2-25 vs distribusi_pi_q2-25.1</t>
+          <t>adhk_pi_q3-25</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Distribusi lebih dari +- 20 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -732,20 +747,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q1-25</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2.515864619582144</v>
+        <v>-9.178222874748657</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>distribusi_net_ekspor_q2-25 vs distribusi_net_ekspor_q2-25.1</t>
+          <t>adhk_net_ekspor_q1-25</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Distribusi lebih dari +- 20 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -764,16 +779,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.962458873350122</v>
+        <v>-25.77125371173042</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>q-to-q_pklnprt_q2-25 vs q-to-q_pklnprt_q2-25.1</t>
+          <t>adhk_net_ekspor_q2-25</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -788,20 +803,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-2.090877037787163</v>
+        <v>-36.46596973894305</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25 vs y-on-y_pkp_q1-25.1</t>
+          <t>adhk_net_ekspor_q3-25</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -820,16 +835,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-2.090877037787163</v>
+        <v>-3.540322088437552</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25 vs c-to-c_pkp_q1-25.1</t>
+          <t>q-to-q_pdrb_q1-25 vs q-to-q_pdrb_q1-25.1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
         </is>
       </c>
     </row>
@@ -844,20 +859,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q1-25</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.2868216146428167</v>
+        <v>2.988567714027034</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q2-25 vs implisit_q-to-q_pkp_q2-25.1</t>
+          <t>q-to-q_pkrt_q1-25 vs q-to-q_pkrt_q1-25.1</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -876,16 +891,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.2525051406646032</v>
+        <v>3.211760562516</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkrt_q1-25 vs implisit_y-on-y_pkrt_q1-25.1</t>
+          <t>q-to-q_pklnprt_q1-25 vs q-to-q_pklnprt_q1-25.1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -900,20 +915,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.8072267675666653</v>
+        <v>1.742413210045948</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pklnprt_q1-25 vs implisit_y-on-y_pklnprt_q1-25.1</t>
+          <t>q-to-q_pklnprt_q2-25 vs q-to-q_pklnprt_q2-25.1</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -928,20 +943,608 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>49.08163234863632</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q2-25 vs q-to-q_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>73</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2.560582700557356</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25 vs q-to-q_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>73</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>q1-25</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>0.8922602908167385</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>implisit_y-on-y_pmtb_q1-25 vs implisit_y-on-y_pmtb_q1-25.1</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+      <c r="D20" t="n">
+        <v>-20.0150934892725</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q1-25 vs q-to-q_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>73</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.34140771505667</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q2-25 vs q-to-q_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>73</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>8.405708297897748</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25 vs q-to-q_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>73</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>5.080694245096408</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25 vs y-on-y_pdrb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,01 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>73</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>3.247559136437268</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25 vs y-on-y_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>73</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>-1.374603337365865</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q1-25 vs y-on-y_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>73</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>-5.844776766673766</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q2-25 vs y-on-y_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>73</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>-2.038233035023034</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25 vs y-on-y_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>73</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>3.987876255417362</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q2-25 vs y-on-y_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>73</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>4.23939926387445</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25 vs y-on-y_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>73</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>-1.374603337365865</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q1-25 vs c-to-c_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>73</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>-4.099702717891911</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q2-25 vs c-to-c_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>73</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2.631933139680763</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25 vs c-to-c_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>73</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1.118170392374992</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25 vs implisit_q-to-q_pkrt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>73</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>-0.8485572719424986</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q1-25 vs implisit_q-to-q_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>73</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>2.900179541294257</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q1-25 vs implisit_q-to-q_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>73</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>-1.066955822626941</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q2-25 vs implisit_q-to-q_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>73</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.739313663483229</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q1-25 vs implisit_q-to-q_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>73</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.06387698139550274</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q1-25 vs implisit_y-on-y_pkrt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>73</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>4.194617489372191</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25 vs implisit_y-on-y_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -956,6 +1559,304 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7312</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Soppeng</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>4.379743246266879</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7312</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Soppeng</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>11.44672678452441</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7312</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Soppeng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.466468246973855</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7312</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Soppeng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.291529193182462</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7312</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Soppeng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.1709027290361635</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7312</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Soppeng</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-3.43840951477388</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7312</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Soppeng</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.239534092564948</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7312</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Soppeng</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3.450414020969573</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7312</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Soppeng</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-2.283321903552035</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -993,11 +1894,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7306</v>
+        <v>7313</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Gowa</t>
+          <t>Kabupaten Wajo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1006,156 +1907,1896 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-4.78707623555107</v>
+        <v>2.238744211092208</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7306</v>
+        <v>7313</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Gowa</t>
+          <t>Kabupaten Wajo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-4.78707623555107</v>
+        <v>10.01526022619615</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7306</v>
+        <v>7313</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Gowa</t>
+          <t>Kabupaten Wajo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.1184378875196671</v>
+        <v>5.836514820405353</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkrt_q1-25_ril vs implisit_y-on-y_pkrt_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7306</v>
+        <v>7313</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Gowa</t>
+          <t>Kabupaten Wajo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.2016257149422624</v>
+        <v>0.7250482142235029</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pklnprt_q1-25_ril vs implisit_y-on-y_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7306</v>
+        <v>7313</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabupaten Gowa</t>
+          <t>Kabupaten Wajo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.7461558698537181</v>
+        <v>21.37037777628638</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pmtb_q1-25_ril vs implisit_y-on-y_pmtb_q1-25_rev</t>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7306</v>
+        <v>7313</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kabupaten Gowa</t>
+          <t>Kabupaten Wajo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>12.52186046505936</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7373</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Palopo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>q1-25</t>
         </is>
       </c>
+      <c r="D2" t="n">
+        <v>3.789102006267799</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7373</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Palopo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>15.73311302582074</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7373</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Palopo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>8.463732297270711</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7373</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Palopo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>12.6993116265144</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7373</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Palopo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7.156610978189351</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7314</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Sidenreng Rappang</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-2.991672575112803</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7314</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Sidenreng Rappang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-8.094227087223071</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7314</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Sidenreng Rappang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>6.690872430663372</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7314</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Sidenreng Rappang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>10.91074290474378</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7314</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Sidenreng Rappang</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-5.041446760283379</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7314</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Sidenreng Rappang</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
       <c r="D7" t="n">
-        <v>-0.225384180916185</v>
+        <v>5.184741111118647</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7314</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Sidenreng Rappang</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>7.41097358077695</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7314</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Sidenreng Rappang</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.1663664407185794</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7315</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Pinrang</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-9.650428592102669</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7315</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Pinrang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-6.385321738515584</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7315</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Pinrang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.6764523201163563</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7315</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Pinrang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-7.000137670290766</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7318</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Tana Toraja</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>10.55443011520341</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7318</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Tana Toraja</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2.454250807330107</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7318</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Tana Toraja</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>21.41970067861061</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7318</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Tana Toraja</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.405744524273568</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7318</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Tana Toraja</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4.305850665047649</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7301</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Selayar</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5102191396969489</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7301</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Selayar</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4.786258666223092</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7301</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Selayar</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-4.040626113709147</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7301</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Selayar</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>5.760087828036772</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7301</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Selayar</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.2591921815802698</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7301</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Selayar</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-2.483579658927934</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7301</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Selayar</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5.348044801042871</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7304</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Jeneponto</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.65271800826584</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7304</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Jeneponto</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2.238092416615504</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7304</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Jeneponto</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.2998604952188714</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7304</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Jeneponto</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3.184300146426095</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7316</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Enrekang</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3408418414590819</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7316</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Enrekang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-26.16526491341198</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7316</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Enrekang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.1572700676711816</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7316</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Enrekang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-19.29047112141792</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7316</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Enrekang</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.5320359921799415</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7316</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Enrekang</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-7.668632175062625</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7316</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Enrekang</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-2.706943153943696</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7325</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu Timur</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.4867973377806466</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7325</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu Timur</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>10.67160008060366</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7325</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu Timur</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>28.55186963362373</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7325</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu Timur</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-10.14698153076781</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7325</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu Timur</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4.334141940140874</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7325</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu Timur</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>19.25373682276797</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7325</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu Timur</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-6.531117017441804</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7325</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu Timur</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-1.87166054865824</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7325</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu Timur</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.2487305503717408</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1170,7 +3811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1207,11 +3848,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7317</v>
+        <v>7372</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Luwu</t>
+          <t>Kota Parepare</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1220,26 +3861,26 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>267291.2391075001</v>
+        <v>-20908.31331250803</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pkp_q1-25_ril vs adhb_pkp_q1-25_rev</t>
+          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7317</v>
+        <v>7372</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Luwu</t>
+          <t>Kota Parepare</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1248,54 +3889,54 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>69839.06237314059</v>
+        <v>-13040.33468221188</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25_ril vs adhb_net_ekspor_q1-25_rev</t>
+          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7317</v>
+        <v>7372</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Luwu</t>
+          <t>Kota Parepare</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4.591734184432123</v>
+        <v>-48209.11434115539</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>distribusi_pkp_q1-25_ril vs distribusi_pkp_q1-25_rev</t>
+          <t>adhk_net_ekspor_q2-25_ril vs adhk_net_ekspor_q2-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Distribusi revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7317</v>
+        <v>7372</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Luwu</t>
+          <t>Kota Parepare</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1304,82 +3945,82 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.327104674043015</v>
+        <v>-46.63750572757339</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkrt_q1-25_ril vs implisit_q-to-q_pkrt_q1-25_rev</t>
+          <t>q-to-q_pkp_q1-25_ril vs q-to-q_pkp_q1-25_rev</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7317</v>
+        <v>7372</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabupaten Luwu</t>
+          <t>Kota Parepare</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9.610465289977185</v>
+        <v>32.85601386499376</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
+          <t>q-to-q_pkp_q2-25_ril vs q-to-q_pkp_q2-25_rev</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7317</v>
+        <v>7372</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kabupaten Luwu</t>
+          <t>Kota Parepare</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.712226669909258</v>
+        <v>11.54462532703555</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkrt_q1-25_ril vs implisit_y-on-y_pkrt_q1-25_rev</t>
+          <t>q-to-q_pmtb_q2-25_ril vs q-to-q_pmtb_q2-25_rev</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7317</v>
+        <v>7372</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kabupaten Luwu</t>
+          <t>Kota Parepare</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1388,16 +4029,1272 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-32.16153485947542</v>
+        <v>14.53105204389044</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkp_q1-25_ril vs implisit_y-on-y_pkp_q1-25_rev</t>
+          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7372</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Parepare</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>14.53105204389044</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7372</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Parepare</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2.343038767325624</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7372</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Parepare</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.1399968779529674</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_net_ekspor_q1-25_ril vs sog_y-on-y_net_ekspor_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7372</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Parepare</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.7244268829677064</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_net_ekspor_q2-25_ril vs sog_y-on-y_net_ekspor_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7372</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Parepare</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-2.52016185926104</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7372</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kota Parepare</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5.483385216286174</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7372</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kota Parepare</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.1683623649299039</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7372</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kota Parepare</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-3.099136239979365</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7372</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kota Parepare</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3.766518264734741</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7372</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kota Parepare</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.03740943530492854</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7372</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kota Parepare</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2.576958280418467</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7371</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Makassar</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.003749245618464559</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7371</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Makassar</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1.420065858303444</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7371</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Makassar</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.6451770283359715</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7303</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Bantaeng</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>6.011879451718555</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7303</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Bantaeng</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1.895398460759295</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7303</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Bantaeng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-5.17084451335369</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7303</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bantaeng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>8.132100705345684</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7303</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Bantaeng</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-2.840991877945153</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7305</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Takalar</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.099616510213094</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7305</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Takalar</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.4042030526474862</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7305</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Takalar</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>7.961010017423121</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7305</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Takalar</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.9055121821997577</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7322</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu Utara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.876926075924516</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7322</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu Utara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-21.12687227668196</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7322</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu Utara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.727455362098851</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7322</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu Utara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-14.74866526568724</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7326</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Toraja Utara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-34.14601730299062</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7326</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Toraja Utara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4.316967258244409</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7326</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Toraja Utara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.849324974302434</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7326</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Toraja Utara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-2.766641193417712</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7326</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Toraja Utara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.2719261843431612</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7326</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Toraja Utara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>35.12874165398024</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25_prov vs implisit_y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7308</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Maros</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1.962698543144185</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7308</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Maros</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.8291752800168783</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1412,7 +5309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1449,197 +5346,169 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7316</v>
+        <v>7306</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Enrekang</t>
+          <t>Kabupaten Gowa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3012.711222989891</v>
+        <v>6235.888989253446</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>adhb_pi_q2-25_ril vs adhb_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7316</v>
+        <v>7306</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Enrekang</t>
+          <t>Kabupaten Gowa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1903.629899938144</v>
+        <v>5306.163372778987</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>adhk_pi_q2-25_ril vs adhk_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7316</v>
+        <v>7306</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Enrekang</t>
+          <t>Kabupaten Gowa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.02079975830800987</v>
+        <v>3.65440404392763</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>y-on-y_pklnprt_q1-25_ril vs y-on-y_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7316</v>
+        <v>7306</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Enrekang</t>
+          <t>Kabupaten Gowa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.02079975830800987</v>
+        <v>-15.45777974210281</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>c-to-c_pklnprt_q1-25_ril vs c-to-c_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7316</v>
+        <v>7306</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabupaten Enrekang</t>
+          <t>Kabupaten Gowa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.04323479294921358</v>
+        <v>3.72734418506374</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7316</v>
+        <v>7306</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kabupaten Enrekang</t>
+          <t>Kabupaten Gowa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.0003746963991223985</v>
+        <v>-4.505365133220633</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pklnprt_q1-25_ril vs sog_y-on-y_pklnprt_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7316</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Kabupaten Enrekang</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0.0464498215506077</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1654,7 +5523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1691,95 +5560,95 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7372</v>
+        <v>7317</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kota Parepare</t>
+          <t>Kabupaten Luwu</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-336.4985360287096</v>
+        <v>-65303.22039072984</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>adhb_net_ekspor_q2-25_ril vs adhb_net_ekspor_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi berlawanan arah</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7372</v>
+        <v>7317</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kota Parepare</t>
+          <t>Kabupaten Luwu</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-209.8712346759998</v>
+        <v>-1.035882823271079</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>distribusi_net_ekspor_q2-25_ril vs distribusi_net_ekspor_q2-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi berlawanan arah</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7372</v>
+        <v>7317</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kota Parepare</t>
+          <t>Kabupaten Luwu</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.01407710397590929</v>
+        <v>12.0627005463534</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>distribusi_pi_q1-25_ril vs distribusi_pi_q1-25_rev</t>
+          <t>implisit_q-to-q_pklnprt_q2-25_ril vs implisit_q-to-q_pklnprt_q2-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Distribusi revisi berlawanan arah</t>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7372</v>
+        <v>7317</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kota Parepare</t>
+          <t>Kabupaten Luwu</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1788,44 +5657,240 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.08995721713925953</v>
+        <v>-0.06578584738724733</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+          <t>implisit_y-on-y_pkrt_q1-25_ril vs implisit_y-on-y_pkrt_q1-25_rev</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7372</v>
+        <v>7317</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kota Parepare</t>
+          <t>Kabupaten Luwu</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>11.66266202173385</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q2-25_ril vs implisit_y-on-y_pklnprt_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7317</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>q1-25</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>-0.07950170033340324</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Growth revisi berlawanan arah</t>
+      <c r="D7" t="n">
+        <v>2.852626506136384</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7317</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.07071607478057285</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_net_ekspor_q2-25_ril vs sog_y-on-y_net_ekspor_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7317</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>15.92367553312372</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7317</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-3.888691858054917</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7317</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-8.436089588542638</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7317</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-1.138084574676178</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7317</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Luwu</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.201733865807015</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1840,7 +5905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1877,11 +5942,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7304</v>
+        <v>7309</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Jeneponto</t>
+          <t>Kabupaten Pangkajene Dan Kepulauan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1890,54 +5955,54 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-659103.2008150599</v>
+        <v>-53.84921158088655</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25_ril vs adhb_net_ekspor_q1-25_rev</t>
+          <t>q-to-q_pkp_q1-25_ril vs q-to-q_pkp_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7304</v>
+        <v>7309</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Jeneponto</t>
+          <t>Kabupaten Pangkajene Dan Kepulauan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-174294.2648441076</v>
+        <v>23.00000906140711</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q1-25_ril vs adhk_net_ekspor_q1-25_rev</t>
+          <t>q-to-q_pkp_q2-25_ril vs q-to-q_pkp_q2-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7304</v>
+        <v>7309</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Jeneponto</t>
+          <t>Kabupaten Pangkajene Dan Kepulauan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1946,26 +6011,26 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6.721587784839238</v>
+        <v>20.40137658140084</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>q-to-q_pdrb_q1-25_ril vs q-to-q_pdrb_q1-25_rev</t>
+          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7304</v>
+        <v>7309</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Jeneponto</t>
+          <t>Kabupaten Pangkajene Dan Kepulauan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1974,44 +6039,156 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.721587784839238</v>
+        <v>20.40137658140084</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>sog_q_pdrb_q1-25_ril vs sog_q_pdrb_q1-25_rev</t>
+          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7304</v>
+        <v>7309</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabupaten Jeneponto</t>
+          <t>Kabupaten Pangkajene Dan Kepulauan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9.267805069173786</v>
+        <v>0.9087611752224347</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>sog_y-on-y_net_ekspor_q1-25_ril vs sog_y-on-y_net_ekspor_q1-25_rev</t>
+          <t>c-to-c_pkp_q2-25_ril vs c-to-c_pkp_q2-25_rev</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7309</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Pangkajene Dan Kepulauan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>16.46067263378826</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7309</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Pangkajene Dan Kepulauan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-7.517915172995372</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7309</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Pangkajene Dan Kepulauan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12.70842828536673</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7309</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Pangkajene Dan Kepulauan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>4.932776064999567</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2026,7 +6203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2063,11 +6240,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7312</v>
+        <v>7311</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Soppeng</t>
+          <t>Kabupaten Bone</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2076,26 +6253,26 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-18132.89685553254</v>
+        <v>0.9727240817362027</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25_ril vs adhb_net_ekspor_q1-25_rev</t>
+          <t>y-on-y_pmtb_q1-25_ril vs y-on-y_pmtb_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7312</v>
+        <v>7311</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Soppeng</t>
+          <t>Kabupaten Bone</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2104,16 +6281,72 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-66271.41179266199</v>
+        <v>0.9727240817362027</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q1-25_ril vs adhk_net_ekspor_q1-25_rev</t>
+          <t>c-to-c_pmtb_q1-25_ril vs c-to-c_pmtb_q1-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7311</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Bone</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3056618131866247</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pmtb_q1-25_ril vs sog_y-on-y_pmtb_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7311</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bone</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6.744039146487417</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2128,7 +6361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2165,11 +6398,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7313</v>
+        <v>7310</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Wajo</t>
+          <t>Kabupaten Barru</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2178,54 +6411,54 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>320824.9448158485</v>
+        <v>0.5737716930928132</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25_ril vs adhb_net_ekspor_q1-25_rev</t>
+          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7313</v>
+        <v>7310</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Wajo</t>
+          <t>Kabupaten Barru</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>129700.3930299492</v>
+        <v>13.00429908346272</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q1-25_ril vs adhk_net_ekspor_q1-25_rev</t>
+          <t>implisit_q-to-q_pkp_q2-25_ril vs implisit_q-to-q_pkp_q2-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7313</v>
+        <v>7310</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Wajo</t>
+          <t>Kabupaten Barru</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2234,72 +6467,100 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.6364222257398929</v>
+        <v>3.439236008352722</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>y-on-y_pmtb_q1-25_ril vs y-on-y_pmtb_q1-25_rev</t>
+          <t>implisit_y-on-y_pkp_q1-25_ril vs implisit_y-on-y_pkp_q1-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7313</v>
+        <v>7310</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Wajo</t>
+          <t>Kabupaten Barru</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.6364222257398929</v>
+        <v>0.3196953013378312</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>c-to-c_pmtb_q1-25_ril vs c-to-c_pmtb_q1-25_rev</t>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7313</v>
+        <v>7310</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabupaten Wajo</t>
+          <t>Kabupaten Barru</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.1813622058989062</v>
+        <v>-5.312634793008129</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pmtb_q1-25_ril vs sog_y-on-y_pmtb_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7310</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Barru</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>6.40614013585441</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2314,7 +6575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2351,11 +6612,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7310</v>
+        <v>7302</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Barru</t>
+          <t>Kabupaten Bulukumba</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2364,212 +6625,240 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6995.248126023071</v>
+        <v>2.233418432362182</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7310</v>
+        <v>7302</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Barru</t>
+          <t>Kabupaten Bulukumba</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-181911.6173272132</v>
+        <v>0.2565160892655144</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q1-25_ril vs adhk_net_ekspor_q1-25_rev</t>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7310</v>
+        <v>7302</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Barru</t>
+          <t>Kabupaten Bulukumba</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.2075957382069052</v>
+        <v>4.609923556912509</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7310</v>
+        <v>7302</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Barru</t>
+          <t>Kabupaten Bulukumba</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.2003497829396</v>
+        <v>-0.02368477762197427</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>y-on-y_pmtb_q1-25_ril vs y-on-y_pmtb_q1-25_rev</t>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7310</v>
+        <v>7302</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabupaten Barru</t>
+          <t>Kabupaten Bulukumba</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.2075957382069052</v>
+        <v>3.460449314067188</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7310</v>
+        <v>7302</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kabupaten Barru</t>
+          <t>Kabupaten Bulukumba</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2.2003497829396</v>
+        <v>2.226574561036305</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>c-to-c_pmtb_q1-25_ril vs c-to-c_pmtb_q1-25_rev</t>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7310</v>
+        <v>7302</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kabupaten Barru</t>
+          <t>Kabupaten Bulukumba</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.01639436129457466</v>
+        <v>2.15710995970066</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7310</v>
+        <v>7302</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kabupaten Barru</t>
+          <t>Kabupaten Bulukumba</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.034521624513574</v>
+        <v>4.370995867091206</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pmtb_q1-25_ril vs sog_y-on-y_pmtb_q1-25_rev</t>
+          <t>sog_q_pi_q3-25</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7302</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Bulukumba</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2.137964308751073</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -2584,7 +6873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2621,11 +6910,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7303</v>
+        <v>7307</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Bantaeng</t>
+          <t>Kabupaten Sinjai</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2634,184 +6923,268 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-27439.33429735503</v>
+        <v>17.30678437707577</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q1-25_ril vs adhk_net_ekspor_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7303</v>
+        <v>7307</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Bantaeng</t>
+          <t>Kabupaten Sinjai</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-4.092243718577147</v>
+        <v>-5.083715323352236</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7303</v>
+        <v>7307</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Bantaeng</t>
+          <t>Kabupaten Sinjai</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.5294165787417775</v>
+        <v>-7.847127353418319</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>y-on-y_pmtb_q1-25_ril vs y-on-y_pmtb_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7303</v>
+        <v>7307</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Bantaeng</t>
+          <t>Kabupaten Sinjai</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-4.092243718577147</v>
+        <v>-1.160320930201826</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7303</v>
+        <v>7307</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabupaten Bantaeng</t>
+          <t>Kabupaten Sinjai</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.5294165787417775</v>
+        <v>5.038291874837729</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>c-to-c_pmtb_q1-25_ril vs c-to-c_pmtb_q1-25_rev</t>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7303</v>
+        <v>7307</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kabupaten Bantaeng</t>
+          <t>Kabupaten Sinjai</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.2687910002585893</v>
+        <v>-4.521091209875025</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7303</v>
+        <v>7307</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kabupaten Bantaeng</t>
+          <t>Kabupaten Sinjai</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.2349575697519805</v>
+        <v>-12.72697896410726</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pmtb_q1-25_ril vs sog_y-on-y_pmtb_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7307</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Sinjai</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.184389686164923</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7307</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Sinjai</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>7.376105497301573</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7307</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Sinjai</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-2.163031241250289</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>

--- a/data/output/evaluasi_73.xlsx
+++ b/data/output/evaluasi_73.xlsx
@@ -844,7 +844,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
